--- a/90_Output/AF_CPG_data_extraction_example(2-39).xlsx
+++ b/90_Output/AF_CPG_data_extraction_example(2-39).xlsx
@@ -499,10 +499,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AV13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="30" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="30" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -738,6 +739,11 @@
       </c>
       <c r="AU1" s="5" t="inlineStr">
         <is>
+          <t>analysis_set</t>
+        </is>
+      </c>
+      <c r="AV1" s="5" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -956,6 +962,7 @@
         </is>
       </c>
       <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1169,6 +1176,7 @@
         </is>
       </c>
       <c r="AU3" s="2" t="n"/>
+      <c r="AV3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1384,6 +1392,7 @@
         </is>
       </c>
       <c r="AU4" s="2" t="n"/>
+      <c r="AV4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1597,6 +1606,7 @@
         </is>
       </c>
       <c r="AU5" s="2" t="n"/>
+      <c r="AV5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1816,6 +1826,13 @@
 outcome 에 IQR 값 있음 -&gt; 변환필요</t>
         </is>
       </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>대규모 다기관 연구
+비교군이 placebo
+outcome 에 IQR 값 있음 -&gt; 변환필요</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -2031,6 +2048,7 @@
         </is>
       </c>
       <c r="AU7" s="2" t="n"/>
+      <c r="AV7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -2244,6 +2262,7 @@
         </is>
       </c>
       <c r="AU8" s="2" t="n"/>
+      <c r="AV8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -2451,6 +2470,7 @@
         </is>
       </c>
       <c r="AU9" s="2" t="n"/>
+      <c r="AV9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -2664,6 +2684,7 @@
         </is>
       </c>
       <c r="AU10" s="8" t="n"/>
+      <c r="AV10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2873,6 +2894,7 @@
         </is>
       </c>
       <c r="AU11" s="2" t="n"/>
+      <c r="AV11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -3088,6 +3110,7 @@
         </is>
       </c>
       <c r="AU12" s="2" t="n"/>
+      <c r="AV12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -3303,6 +3326,11 @@
         </is>
       </c>
       <c r="AU13" s="2" t="inlineStr">
+        <is>
+          <t>치료기간 명시 없음. 자감초탕과 귀비탕 복용횟수 차이있음</t>
+        </is>
+      </c>
+      <c r="AV13" s="2" t="inlineStr">
         <is>
           <t>치료기간 명시 없음. 자감초탕과 귀비탕 복용횟수 차이있음</t>
         </is>

--- a/90_Output/AF_CPG_data_extraction_example(2-39).xlsx
+++ b/90_Output/AF_CPG_data_extraction_example(2-39).xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기본정보" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="아웃컴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="한의중재_한약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20437,4 +20438,70 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>last_upgrade</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>last_actor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>